--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-slot-presence-absence.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-slot-presence-absence.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-04T09:38:55+00:00</t>
+    <t>2026-03-04T10:43:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4152,7 +4152,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>88</v>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-slot-presence-absence.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-slot-presence-absence.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-04T10:43:17+00:00</t>
+    <t>2026-03-04T13:55:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-slot-presence-absence.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-slot-presence-absence.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1393" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1567" uniqueCount="321">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-04T13:55:47+00:00</t>
+    <t>2026-03-05T13:54:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -612,10 +612,36 @@
     <t>Slot.extension</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
   </si>
   <si>
     <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>Slot.extension:TDDUIPlannedAbsence</t>
+  </si>
+  <si>
+    <t>TDDUIPlannedAbsence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-planned-absence}
+</t>
+  </si>
+  <si>
+    <t>TDDUI Planned Absence</t>
+  </si>
+  <si>
+    <t>Absence prévue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>absencePrevue</t>
   </si>
   <si>
     <t>Slot.modifierExtension</t>
@@ -879,7 +905,50 @@
     <t>http://hl7.org/fhir/ValueSet/slotstatus</t>
   </si>
   <si>
+    <t>Statut.statut</t>
+  </si>
+  <si>
     <t>FREEBUSY;FBTYPE=(freeBusyType):19980314T233000Z/19980315T003000Z If the freeBusyType is BUSY, then this value can be excluded</t>
+  </si>
+  <si>
+    <t>Slot.status.id</t>
+  </si>
+  <si>
+    <t>xml:id (or equivalent in JSON)</t>
+  </si>
+  <si>
+    <t>unique id for the element within a resource (for internal references)</t>
+  </si>
+  <si>
+    <t>Slot.status.extension</t>
+  </si>
+  <si>
+    <t>Slot.status.extension:TDDUIStatusAuthor</t>
+  </si>
+  <si>
+    <t>TDDUIStatusAuthor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-status-author}
+</t>
+  </si>
+  <si>
+    <t>TDDUI Status Author</t>
+  </si>
+  <si>
+    <t>Extension permettant de représenter l'auteur du statut.</t>
+  </si>
+  <si>
+    <t>Statut.auteur</t>
+  </si>
+  <si>
+    <t>Slot.status.value</t>
+  </si>
+  <si>
+    <t>Primitive value for code</t>
+  </si>
+  <si>
+    <t>string.value</t>
   </si>
   <si>
     <t>Slot.start</t>
@@ -1239,12 +1308,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN38"/>
+  <dimension ref="A1:AN43"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="23.76171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="33.25" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="19.65234375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="18.87890625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1252,7 +1321,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="70.6796875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="78.1015625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -3234,7 +3303,7 @@
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3256,14 +3325,12 @@
         <v>108</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>109</v>
+        <v>192</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>77</v>
@@ -3300,19 +3367,17 @@
         <v>77</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC18" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="AC18" s="2"/>
       <c r="AD18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3330,7 +3395,7 @@
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>190</v>
+        <v>77</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
@@ -3341,46 +3406,44 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="C19" s="2"/>
+        <v>191</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>196</v>
+      </c>
       <c r="D19" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>108</v>
+        <v>197</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>77</v>
       </c>
@@ -3428,7 +3491,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3437,16 +3500,16 @@
         <v>79</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>77</v>
+        <v>200</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>116</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>77</v>
+        <v>201</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>190</v>
+        <v>77</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -3457,42 +3520,46 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>200</v>
+        <v>108</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
+        <v>204</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>205</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>77</v>
       </c>
@@ -3540,7 +3607,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3552,27 +3619,27 @@
         <v>77</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>203</v>
+        <v>77</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>77</v>
+        <v>190</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>204</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3580,7 +3647,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>88</v>
@@ -3592,16 +3659,16 @@
         <v>77</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>102</v>
+        <v>208</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>103</v>
+        <v>209</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>104</v>
+        <v>210</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3652,50 +3719,50 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>105</v>
+        <v>207</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>77</v>
+        <v>211</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>77</v>
+        <v>212</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>77</v>
@@ -3707,17 +3774,15 @@
         <v>77</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -3754,31 +3819,31 @@
         <v>77</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>77</v>
@@ -3795,46 +3860,44 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>167</v>
+        <v>108</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>208</v>
+        <v>109</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>209</v>
+        <v>110</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>211</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>77</v>
       </c>
@@ -3858,47 +3921,49 @@
         <v>77</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="Y23" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z23" t="s" s="2">
-        <v>213</v>
+        <v>77</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>214</v>
+        <v>115</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>215</v>
+        <v>85</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
@@ -3909,10 +3974,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3929,25 +3994,25 @@
         <v>77</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -3972,31 +4037,29 @@
         <v>77</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="Y24" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="Y24" s="2"/>
+      <c r="Z24" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF24" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="Z24" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="AA24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF24" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4014,7 +4077,7 @@
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
@@ -4025,10 +4088,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4036,7 +4099,7 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>88</v>
@@ -4051,7 +4114,7 @@
         <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>129</v>
+        <v>225</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>226</v>
@@ -4073,28 +4136,28 @@
         <v>77</v>
       </c>
       <c r="S25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X25" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="Y25" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="T25" t="s" s="2">
+      <c r="Z25" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="U25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z25" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>77</v>
@@ -4130,7 +4193,7 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -4141,10 +4204,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4167,18 +4230,20 @@
         <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>77</v>
       </c>
@@ -4187,10 +4252,10 @@
         <v>77</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>77</v>
+        <v>238</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="U26" t="s" s="2">
         <v>77</v>
@@ -4226,7 +4291,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4244,7 +4309,7 @@
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4255,10 +4320,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4266,7 +4331,7 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>88</v>
@@ -4281,7 +4346,7 @@
         <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>242</v>
+        <v>102</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>243</v>
@@ -4289,7 +4354,9 @@
       <c r="M27" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="N27" s="2"/>
+      <c r="N27" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4302,7 +4369,7 @@
         <v>77</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>77</v>
+        <v>246</v>
       </c>
       <c r="U27" t="s" s="2">
         <v>77</v>
@@ -4338,7 +4405,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4356,7 +4423,7 @@
         <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
@@ -4367,10 +4434,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4393,17 +4460,15 @@
         <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>251</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>77</v>
@@ -4452,7 +4517,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4470,7 +4535,7 @@
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
@@ -4481,10 +4546,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4507,15 +4572,17 @@
         <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>217</v>
+        <v>256</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>77</v>
@@ -4540,11 +4607,13 @@
         <v>77</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="Y29" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z29" t="s" s="2">
-        <v>257</v>
+        <v>77</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>77</v>
@@ -4562,13 +4631,13 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>77</v>
@@ -4580,21 +4649,21 @@
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>77</v>
+        <v>261</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>258</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4605,7 +4674,7 @@
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>77</v>
@@ -4617,13 +4686,13 @@
         <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4654,25 +4723,25 @@
       </c>
       <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF30" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>259</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4696,15 +4765,15 @@
         <v>77</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>258</v>
+        <v>266</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4727,13 +4796,13 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4760,11 +4829,11 @@
         <v>77</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>212</v>
+        <v>157</v>
       </c>
       <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>77</v>
@@ -4782,7 +4851,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -4806,15 +4875,15 @@
         <v>77</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>258</v>
+        <v>266</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4825,7 +4894,7 @@
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>77</v>
@@ -4837,13 +4906,13 @@
         <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4870,11 +4939,11 @@
         <v>77</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>171</v>
+        <v>220</v>
       </c>
       <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>77</v>
@@ -4892,13 +4961,13 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>77</v>
@@ -4916,15 +4985,15 @@
         <v>77</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>258</v>
+        <v>266</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4932,7 +5001,7 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>88</v>
@@ -4947,13 +5016,13 @@
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>272</v>
+        <v>225</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4980,13 +5049,11 @@
         <v>77</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y33" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>77</v>
+        <v>278</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>77</v>
@@ -5004,10 +5071,10 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>88</v>
@@ -5028,15 +5095,15 @@
         <v>77</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>77</v>
+        <v>266</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5059,13 +5126,13 @@
         <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>167</v>
+        <v>280</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5092,11 +5159,13 @@
         <v>77</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="Y34" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z34" t="s" s="2">
-        <v>278</v>
+        <v>77</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>77</v>
@@ -5114,7 +5183,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>88</v>
@@ -5135,7 +5204,7 @@
         <v>77</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>279</v>
+        <v>77</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>77</v>
@@ -5143,10 +5212,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5169,13 +5238,13 @@
         <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>123</v>
+        <v>167</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5202,13 +5271,11 @@
         <v>77</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>77</v>
+        <v>286</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>77</v>
@@ -5226,7 +5293,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>88</v>
@@ -5241,24 +5308,24 @@
         <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>285</v>
+        <v>77</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5266,7 +5333,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>88</v>
@@ -5278,16 +5345,16 @@
         <v>77</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5338,10 +5405,10 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>286</v>
+        <v>105</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>88</v>
@@ -5350,27 +5417,27 @@
         <v>77</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>289</v>
+        <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>290</v>
+        <v>77</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>285</v>
+        <v>77</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5378,10 +5445,10 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>77</v>
@@ -5393,22 +5460,20 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>292</v>
+        <v>108</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>293</v>
+        <v>192</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>294</v>
+        <v>193</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q37" t="s" s="2">
-        <v>295</v>
-      </c>
+      <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
         <v>77</v>
       </c>
@@ -5440,31 +5505,29 @@
         <v>77</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="AC37" s="2"/>
       <c r="AD37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>291</v>
+        <v>115</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>77</v>
@@ -5481,18 +5544,20 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="C38" s="2"/>
+        <v>292</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>294</v>
+      </c>
       <c r="D38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>88</v>
@@ -5507,13 +5572,13 @@
         <v>77</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>102</v>
+        <v>295</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5564,30 +5629,592 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>296</v>
+        <v>115</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>77</v>
+        <v>200</v>
       </c>
       <c r="AJ38" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN38" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E39" s="2"/>
+      <c r="F39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K39" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
+      <c r="P39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q39" s="2"/>
+      <c r="R39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J40" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K40" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
+      <c r="P40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q40" s="2"/>
+      <c r="R40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AK38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN38" t="s" s="2">
+      <c r="AK40" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
+      <c r="P41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q41" s="2"/>
+      <c r="R41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AN41" t="s" s="2">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K42" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
+      <c r="P42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q42" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="R42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K43" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
+      <c r="P43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q43" s="2"/>
+      <c r="R43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN43" t="s" s="2">
         <v>77</v>
       </c>
     </row>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-slot-presence-absence.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-slot-presence-absence.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T13:54:22+00:00</t>
+    <t>2026-03-05T14:12:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-slot-presence-absence.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-slot-presence-absence.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T14:12:55+00:00</t>
+    <t>2026-03-05T15:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -755,7 +755,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>https://identifiant-medicosocial-presence-absence.esante.gouv.fr</t>
+    <t>https://identifiant-medicosocial-presenceabsence.esante.gouv.fr</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -5445,7 +5445,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>79</v>
@@ -5557,7 +5557,7 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>88</v>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-slot-presence-absence.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-slot-presence-absence.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T15:01:37+00:00</t>
+    <t>2026-03-05T15:27:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-slot-presence-absence.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-slot-presence-absence.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1567" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1567" uniqueCount="323">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T15:27:35+00:00</t>
+    <t>2026-03-05T16:09:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -856,6 +856,9 @@
     <t>http://hl7.org/fhir/ValueSet/service-type</t>
   </si>
   <si>
+    <t>typePresenceAbsence</t>
+  </si>
+  <si>
     <t>Slot.specialty</t>
   </si>
   <si>
@@ -878,6 +881,9 @@
   </si>
   <si>
     <t>http://terminology.hl7.org/ValueSet/v2-0276</t>
+  </si>
+  <si>
+    <t>motifAbsence</t>
   </si>
   <si>
     <t>Slot.schedule</t>
@@ -4866,7 +4872,7 @@
         <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>77</v>
+        <v>271</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>77</v>
@@ -4880,10 +4886,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4909,10 +4915,10 @@
         <v>225</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4943,7 +4949,7 @@
       </c>
       <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>77</v>
@@ -4961,7 +4967,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -4990,10 +4996,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5019,10 +5025,10 @@
         <v>225</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5053,7 +5059,7 @@
       </c>
       <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>77</v>
@@ -5071,7 +5077,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5086,7 +5092,7 @@
         <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>77</v>
+        <v>280</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>77</v>
@@ -5100,10 +5106,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5126,13 +5132,13 @@
         <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5183,7 +5189,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>88</v>
@@ -5212,10 +5218,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5241,10 +5247,10 @@
         <v>167</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5275,7 +5281,7 @@
       </c>
       <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>77</v>
@@ -5293,7 +5299,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>88</v>
@@ -5308,13 +5314,13 @@
         <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>77</v>
@@ -5322,10 +5328,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5351,10 +5357,10 @@
         <v>102</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5434,10 +5440,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5544,13 +5550,13 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D38" t="s" s="2">
         <v>77</v>
@@ -5572,13 +5578,13 @@
         <v>77</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5644,7 +5650,7 @@
         <v>116</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>77</v>
@@ -5658,10 +5664,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5687,10 +5693,10 @@
         <v>102</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5741,7 +5747,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -5770,10 +5776,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5799,10 +5805,10 @@
         <v>123</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5853,7 +5859,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>88</v>
@@ -5868,24 +5874,24 @@
         <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5911,10 +5917,10 @@
         <v>123</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5965,7 +5971,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>88</v>
@@ -5980,24 +5986,24 @@
         <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6020,13 +6026,13 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6034,7 +6040,7 @@
         <v>77</v>
       </c>
       <c r="Q42" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="R42" t="s" s="2">
         <v>77</v>
@@ -6079,7 +6085,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6108,10 +6114,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6137,10 +6143,10 @@
         <v>102</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6191,7 +6197,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-slot-presence-absence.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-slot-presence-absence.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T16:09:12+00:00</t>
+    <t>2026-03-06T08:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-slot-presence-absence.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-slot-presence-absence.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T08:12:50+00:00</t>
+    <t>2026-03-09T13:07:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-slot-presence-absence.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-slot-presence-absence.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1567" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1567" uniqueCount="324">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T13:07:52+00:00</t>
+    <t>2026-03-17T10:53:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -410,6 +410,9 @@
     <t>Meta.lastUpdated</t>
   </si>
   <si>
+    <t>Statut.dateStatut</t>
+  </si>
+  <si>
     <t>Slot.meta.source</t>
   </si>
   <si>
@@ -631,7 +634,7 @@
 </t>
   </si>
   <si>
-    <t>TDDUI Planned Absence</t>
+    <t>Indique si l'absence est prévue ou non.</t>
   </si>
   <si>
     <t>Absence prévue</t>
@@ -939,7 +942,7 @@
 </t>
   </si>
   <si>
-    <t>TDDUI Status Author</t>
+    <t>Auteur du statut.</t>
   </si>
   <si>
     <t>Extension permettant de représenter l'auteur du statut.</t>
@@ -2260,7 +2263,7 @@
         <v>100</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="AL8" t="s" s="2">
         <v>77</v>
@@ -2274,10 +2277,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2300,16 +2303,16 @@
         <v>89</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2359,7 +2362,7 @@
         <v>77</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2388,10 +2391,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2414,16 +2417,16 @@
         <v>89</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2461,10 +2464,10 @@
         <v>77</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AD10" t="s" s="2">
         <v>77</v>
@@ -2473,7 +2476,7 @@
         <v>114</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2502,13 +2505,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>77</v>
@@ -2530,16 +2533,16 @@
         <v>89</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2589,7 +2592,7 @@
         <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2618,10 +2621,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2644,16 +2647,16 @@
         <v>89</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -2679,13 +2682,13 @@
         <v>77</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>77</v>
@@ -2703,7 +2706,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2732,10 +2735,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2758,16 +2761,16 @@
         <v>89</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2793,13 +2796,13 @@
         <v>77</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>77</v>
@@ -2817,7 +2820,7 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -2846,10 +2849,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2872,16 +2875,16 @@
         <v>89</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2931,7 +2934,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -2960,10 +2963,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2986,16 +2989,16 @@
         <v>77</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3021,13 +3024,13 @@
         <v>77</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>77</v>
@@ -3045,7 +3048,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3074,14 +3077,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3100,16 +3103,16 @@
         <v>77</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3159,7 +3162,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3177,7 +3180,7 @@
         <v>77</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>77</v>
@@ -3188,14 +3191,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3214,16 +3217,16 @@
         <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3273,7 +3276,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3291,7 +3294,7 @@
         <v>77</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>77</v>
@@ -3302,10 +3305,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3331,10 +3334,10 @@
         <v>108</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3383,7 +3386,7 @@
         <v>114</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3412,13 +3415,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>77</v>
@@ -3440,13 +3443,13 @@
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3497,7 +3500,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3506,13 +3509,13 @@
         <v>79</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>116</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>77</v>
@@ -3526,10 +3529,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3555,16 +3558,16 @@
         <v>108</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N20" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>77</v>
@@ -3613,7 +3616,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3631,7 +3634,7 @@
         <v>77</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>77</v>
@@ -3642,10 +3645,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3668,13 +3671,13 @@
         <v>89</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3725,7 +3728,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3740,7 +3743,7 @@
         <v>100</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>77</v>
@@ -3749,15 +3752,15 @@
         <v>77</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3866,10 +3869,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3980,10 +3983,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4006,19 +4009,19 @@
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -4043,11 +4046,11 @@
         <v>77</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>77</v>
@@ -4065,7 +4068,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4083,7 +4086,7 @@
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
@@ -4094,10 +4097,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4120,19 +4123,19 @@
         <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4157,13 +4160,13 @@
         <v>77</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>77</v>
@@ -4181,7 +4184,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4199,7 +4202,7 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -4210,10 +4213,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4236,19 +4239,19 @@
         <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4258,10 +4261,10 @@
         <v>77</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="U26" t="s" s="2">
         <v>77</v>
@@ -4297,7 +4300,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4315,7 +4318,7 @@
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4326,10 +4329,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4355,13 +4358,13 @@
         <v>102</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4375,7 +4378,7 @@
         <v>77</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="U27" t="s" s="2">
         <v>77</v>
@@ -4411,7 +4414,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4429,7 +4432,7 @@
         <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
@@ -4440,10 +4443,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4466,13 +4469,13 @@
         <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4523,7 +4526,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4541,7 +4544,7 @@
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
@@ -4552,10 +4555,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4578,16 +4581,16 @@
         <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4637,7 +4640,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4655,7 +4658,7 @@
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
@@ -4666,10 +4669,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4692,13 +4695,13 @@
         <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4725,11 +4728,11 @@
         <v>77</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>77</v>
@@ -4747,7 +4750,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4771,15 +4774,15 @@
         <v>77</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4802,13 +4805,13 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4835,11 +4838,11 @@
         <v>77</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>77</v>
@@ -4857,7 +4860,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -4872,7 +4875,7 @@
         <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>77</v>
@@ -4881,15 +4884,15 @@
         <v>77</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4912,13 +4915,13 @@
         <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4945,11 +4948,11 @@
         <v>77</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>77</v>
@@ -4967,7 +4970,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -4991,15 +4994,15 @@
         <v>77</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5022,13 +5025,13 @@
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5055,11 +5058,11 @@
         <v>77</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>77</v>
@@ -5077,7 +5080,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5092,7 +5095,7 @@
         <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>77</v>
@@ -5101,15 +5104,15 @@
         <v>77</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5132,13 +5135,13 @@
         <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5189,7 +5192,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>88</v>
@@ -5218,10 +5221,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5244,13 +5247,13 @@
         <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5277,11 +5280,11 @@
         <v>77</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>77</v>
@@ -5299,7 +5302,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>88</v>
@@ -5314,13 +5317,13 @@
         <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>77</v>
@@ -5328,10 +5331,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5357,10 +5360,10 @@
         <v>102</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5440,10 +5443,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5469,10 +5472,10 @@
         <v>108</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5550,13 +5553,13 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="B38" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="B38" t="s" s="2">
-        <v>294</v>
-      </c>
       <c r="C38" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D38" t="s" s="2">
         <v>77</v>
@@ -5578,13 +5581,13 @@
         <v>77</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5644,13 +5647,13 @@
         <v>79</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>116</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>77</v>
@@ -5664,10 +5667,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5693,10 +5696,10 @@
         <v>102</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5747,7 +5750,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -5776,10 +5779,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5805,10 +5808,10 @@
         <v>123</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5859,7 +5862,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>88</v>
@@ -5874,24 +5877,24 @@
         <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5917,10 +5920,10 @@
         <v>123</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5971,7 +5974,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>88</v>
@@ -5986,24 +5989,24 @@
         <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6026,13 +6029,13 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6040,7 +6043,7 @@
         <v>77</v>
       </c>
       <c r="Q42" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="R42" t="s" s="2">
         <v>77</v>
@@ -6085,7 +6088,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6114,10 +6117,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6143,10 +6146,10 @@
         <v>102</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6197,7 +6200,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-slot-presence-absence.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-slot-presence-absence.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T10:53:05+00:00</t>
+    <t>2026-06-03T14:26:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -856,7 +856,7 @@
     <t>The type of appointments that can be booked into this slot (ideally this would be an identifiable service - which is at a location, rather than the location itself). If provided then this overrides the value provided on the availability resource.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/service-type</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-j405-type-presence-absence-ms</t>
   </si>
   <si>
     <t>typePresenceAbsence</t>
@@ -1345,7 +1345,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="52.66796875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="60.9453125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -4790,10 +4790,10 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>77</v>
@@ -4838,7 +4838,7 @@
         <v>77</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>158</v>
+        <v>221</v>
       </c>
       <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-slot-presence-absence.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-slot-presence-absence.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1567" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1890" uniqueCount="336">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T14:26:22+00:00</t>
+    <t>2026-06-09T13:44:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -676,6 +676,10 @@
     <t>External Ids for this item.</t>
   </si>
   <si>
+    <t xml:space="preserve">pattern:type}
+</t>
+  </si>
+  <si>
     <t>idPresenceAbsenceUsager</t>
   </si>
   <si>
@@ -758,9 +762,6 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>https://identifiant-medicosocial-presenceabsence.esante.gouv.fr</t>
-  </si>
-  <si>
     <t>http://www.acme.com/identifiers/patient</t>
   </si>
   <si>
@@ -830,6 +831,47 @@
   </si>
   <si>
     <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
+  </si>
+  <si>
+    <t>Slot.identifier:idPA</t>
+  </si>
+  <si>
+    <t>idPA</t>
+  </si>
+  <si>
+    <t>Slot.identifier:idPA.id</t>
+  </si>
+  <si>
+    <t>Slot.identifier:idPA.extension</t>
+  </si>
+  <si>
+    <t>Slot.identifier:idPA.use</t>
+  </si>
+  <si>
+    <t>Slot.identifier:idPA.type</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-slot-identifier"/&gt;
+    &lt;code value="PA"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>Slot.identifier:idPA.system</t>
+  </si>
+  <si>
+    <t>https://identifiant-medicosocial-presenceabsence.esante.gouv.fr</t>
+  </si>
+  <si>
+    <t>Slot.identifier:idPA.value</t>
+  </si>
+  <si>
+    <t>Slot.identifier:idPA.period</t>
+  </si>
+  <si>
+    <t>Slot.identifier:idPA.assigner</t>
   </si>
   <si>
     <t>Slot.serviceCategory</t>
@@ -1317,7 +1359,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN43"/>
+  <dimension ref="A1:AN52"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="33.25" customWidth="true" bestFit="true"/>
@@ -3659,7 +3701,7 @@
         <v>88</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>77</v>
@@ -3716,16 +3758,14 @@
         <v>77</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="AC21" s="2"/>
       <c r="AD21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AF21" t="s" s="2">
         <v>208</v>
@@ -3743,7 +3783,7 @@
         <v>100</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>77</v>
@@ -3752,15 +3792,15 @@
         <v>77</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3869,10 +3909,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3983,10 +4023,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4012,16 +4052,16 @@
         <v>168</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -4046,11 +4086,11 @@
         <v>77</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>77</v>
@@ -4068,7 +4108,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4086,7 +4126,7 @@
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
@@ -4097,10 +4137,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4123,19 +4163,19 @@
         <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4163,10 +4203,10 @@
         <v>150</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>77</v>
@@ -4184,7 +4224,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4202,7 +4242,7 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -4213,10 +4253,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4224,7 +4264,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>88</v>
@@ -4242,16 +4282,16 @@
         <v>130</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4261,7 +4301,7 @@
         <v>77</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>239</v>
+        <v>77</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>240</v>
@@ -4340,7 +4380,7 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>88</v>
@@ -4672,15 +4712,17 @@
         <v>263</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="C30" s="2"/>
+        <v>208</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>264</v>
+      </c>
       <c r="D30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>88</v>
@@ -4695,13 +4737,13 @@
         <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>226</v>
+        <v>209</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>264</v>
+        <v>210</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>265</v>
+        <v>211</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4728,11 +4770,13 @@
         <v>77</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="Y30" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z30" t="s" s="2">
-        <v>266</v>
+        <v>77</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>77</v>
@@ -4750,7 +4794,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>263</v>
+        <v>208</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4774,15 +4818,15 @@
         <v>77</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>267</v>
+        <v>214</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>268</v>
+        <v>215</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4790,7 +4834,7 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>88</v>
@@ -4802,16 +4846,16 @@
         <v>77</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>226</v>
+        <v>102</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>269</v>
+        <v>103</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>270</v>
+        <v>104</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4838,11 +4882,13 @@
         <v>77</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="Y31" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z31" t="s" s="2">
-        <v>271</v>
+        <v>77</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>77</v>
@@ -4860,43 +4906,43 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>268</v>
+        <v>105</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>272</v>
+        <v>77</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>267</v>
+        <v>77</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -4912,18 +4958,20 @@
         <v>77</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>226</v>
+        <v>108</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>274</v>
+        <v>109</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>77</v>
@@ -4948,29 +4996,31 @@
         <v>77</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="Y32" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z32" t="s" s="2">
-        <v>276</v>
+        <v>77</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>273</v>
+        <v>115</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -4982,27 +5032,27 @@
         <v>77</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>267</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>277</v>
+        <v>217</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5019,22 +5069,26 @@
         <v>77</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J33" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>226</v>
+        <v>168</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>278</v>
+        <v>218</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
+        <v>219</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
       </c>
@@ -5058,11 +5112,11 @@
         <v>77</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>172</v>
+        <v>222</v>
       </c>
       <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>280</v>
+        <v>223</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>77</v>
@@ -5080,7 +5134,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>277</v>
+        <v>224</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5095,24 +5149,24 @@
         <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>281</v>
+        <v>77</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>77</v>
+        <v>225</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>267</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>282</v>
+        <v>268</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>282</v>
+        <v>226</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5135,16 +5189,20 @@
         <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>283</v>
+        <v>227</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>284</v>
+        <v>228</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
+        <v>229</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
       </c>
@@ -5153,7 +5211,7 @@
         <v>77</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>77</v>
+        <v>269</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>77</v>
@@ -5168,13 +5226,13 @@
         <v>77</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>77</v>
+        <v>232</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>77</v>
+        <v>233</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>77</v>
@@ -5192,10 +5250,10 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>282</v>
+        <v>234</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>88</v>
@@ -5210,7 +5268,7 @@
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>77</v>
+        <v>225</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
@@ -5221,10 +5279,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>286</v>
+        <v>270</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>286</v>
+        <v>235</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5247,16 +5305,20 @@
         <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>168</v>
+        <v>130</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>287</v>
+        <v>236</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
+        <v>237</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>239</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
       </c>
@@ -5265,10 +5327,10 @@
         <v>77</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>77</v>
+        <v>271</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>77</v>
+        <v>240</v>
       </c>
       <c r="U35" t="s" s="2">
         <v>77</v>
@@ -5280,11 +5342,13 @@
         <v>77</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="Y35" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z35" t="s" s="2">
-        <v>289</v>
+        <v>77</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>77</v>
@@ -5302,10 +5366,10 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>286</v>
+        <v>241</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>88</v>
@@ -5317,13 +5381,13 @@
         <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>290</v>
+        <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>77</v>
+        <v>242</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>291</v>
+        <v>77</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>77</v>
@@ -5331,10 +5395,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>292</v>
+        <v>272</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>292</v>
+        <v>243</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5342,7 +5406,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>88</v>
@@ -5354,18 +5418,20 @@
         <v>77</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
         <v>102</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>293</v>
+        <v>244</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>245</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5378,7 +5444,7 @@
         <v>77</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>77</v>
+        <v>247</v>
       </c>
       <c r="U36" t="s" s="2">
         <v>77</v>
@@ -5414,7 +5480,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>105</v>
+        <v>248</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5426,13 +5492,13 @@
         <v>77</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>77</v>
+        <v>249</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
@@ -5443,10 +5509,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>295</v>
+        <v>273</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>295</v>
+        <v>250</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5457,7 +5523,7 @@
         <v>78</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>77</v>
@@ -5466,16 +5532,16 @@
         <v>77</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>108</v>
+        <v>251</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>193</v>
+        <v>252</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>194</v>
+        <v>253</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5514,35 +5580,37 @@
         <v>77</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AC37" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="AD37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>115</v>
+        <v>254</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>77</v>
+        <v>255</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>77</v>
@@ -5553,14 +5621,12 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>296</v>
+        <v>274</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="C38" t="s" s="2">
-        <v>297</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>77</v>
       </c>
@@ -5578,18 +5644,20 @@
         <v>77</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>299</v>
+        <v>258</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>77</v>
@@ -5638,25 +5706,25 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>115</v>
+        <v>261</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>201</v>
+        <v>77</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>301</v>
+        <v>77</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>77</v>
+        <v>262</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>77</v>
@@ -5667,10 +5735,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>302</v>
+        <v>275</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>302</v>
+        <v>275</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5690,16 +5758,16 @@
         <v>77</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>102</v>
+        <v>227</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>303</v>
+        <v>276</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>303</v>
+        <v>277</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5726,13 +5794,11 @@
         <v>77</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="Y39" s="2"/>
       <c r="Z39" t="s" s="2">
-        <v>77</v>
+        <v>278</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>77</v>
@@ -5750,19 +5816,19 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>304</v>
+        <v>275</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>77</v>
@@ -5774,15 +5840,15 @@
         <v>77</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>77</v>
+        <v>279</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>305</v>
+        <v>280</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>305</v>
+        <v>280</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5805,13 +5871,13 @@
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>123</v>
+        <v>227</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>306</v>
+        <v>281</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5838,13 +5904,11 @@
         <v>77</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y40" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>77</v>
+        <v>283</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>77</v>
@@ -5862,13 +5926,13 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>305</v>
+        <v>280</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>77</v>
@@ -5877,24 +5941,24 @@
         <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>309</v>
+        <v>77</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>310</v>
+        <v>279</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>311</v>
+        <v>285</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>311</v>
+        <v>285</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5902,10 +5966,10 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>77</v>
@@ -5917,13 +5981,13 @@
         <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>123</v>
+        <v>227</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>312</v>
+        <v>286</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>313</v>
+        <v>287</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5950,13 +6014,11 @@
         <v>77</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y41" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="Y41" s="2"/>
       <c r="Z41" t="s" s="2">
-        <v>77</v>
+        <v>288</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>77</v>
@@ -5974,13 +6036,13 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>311</v>
+        <v>285</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>77</v>
@@ -5989,24 +6051,24 @@
         <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>314</v>
+        <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>315</v>
+        <v>77</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>310</v>
+        <v>279</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>316</v>
+        <v>289</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>316</v>
+        <v>289</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6026,25 +6088,23 @@
         <v>77</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>317</v>
+        <v>227</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>318</v>
+        <v>290</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>319</v>
+        <v>291</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q42" t="s" s="2">
-        <v>320</v>
-      </c>
+      <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
         <v>77</v>
       </c>
@@ -6064,13 +6124,11 @@
         <v>77</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y42" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>77</v>
+        <v>292</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>77</v>
@@ -6088,7 +6146,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>316</v>
+        <v>289</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6103,7 +6161,7 @@
         <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>77</v>
+        <v>293</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>77</v>
@@ -6112,15 +6170,15 @@
         <v>77</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>77</v>
+        <v>279</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>321</v>
+        <v>294</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>321</v>
+        <v>294</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6128,7 +6186,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>88</v>
@@ -6140,16 +6198,16 @@
         <v>77</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>102</v>
+        <v>295</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>322</v>
+        <v>296</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>323</v>
+        <v>297</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6200,10 +6258,10 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>321</v>
+        <v>294</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>88</v>
@@ -6224,6 +6282,1014 @@
         <v>77</v>
       </c>
       <c r="AN43" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
+      <c r="P44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="Y44" s="2"/>
+      <c r="Z44" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
+      <c r="P45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
+      <c r="P46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="AC46" s="2"/>
+      <c r="AD46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="C47" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="D47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
+      <c r="P47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
+      <c r="P48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q48" s="2"/>
+      <c r="R48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
+      <c r="P49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
+      <c r="P50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
+      <c r="P51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q51" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="R51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
+      <c r="P52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>77</v>
       </c>
     </row>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-slot-presence-absence.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-slot-presence-absence.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1890" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1890" uniqueCount="338">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T13:44:39+00:00</t>
+    <t>2026-06-11T13:38:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -837,6 +837,13 @@
   </si>
   <si>
     <t>idPA</t>
+  </si>
+  <si>
+    <t>Identifiant de présence/absence</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+SlotPresenceAbsenceIdentifierFormat:l'identifiant de la présence/absence doit respecter le format : 3+FINESS/identifiantLocalUsagerESSMS-PA-numPresenceAbsenceUsager {value.matches('^3[0-9]{9}/[A-Za-z0-9]+-PA-[A-Za-z0-9]+$')}</t>
   </si>
   <si>
     <t>Slot.identifier:idPA.id</t>
@@ -925,7 +932,7 @@
     <t>The style of appointment or patient that may be booked in the slot (not service type).</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0276</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-j406-motif-absence-ms</t>
   </si>
   <si>
     <t>motifAbsence</t>
@@ -4740,7 +4747,7 @@
         <v>209</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>210</v>
+        <v>265</v>
       </c>
       <c r="M30" t="s" s="2">
         <v>211</v>
@@ -4806,7 +4813,7 @@
         <v>77</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>100</v>
+        <v>266</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>77</v>
@@ -4823,7 +4830,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>215</v>
@@ -4935,7 +4942,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>216</v>
@@ -5049,7 +5056,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>217</v>
@@ -5163,7 +5170,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>226</v>
@@ -5211,7 +5218,7 @@
         <v>77</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>77</v>
@@ -5279,7 +5286,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>235</v>
@@ -5327,7 +5334,7 @@
         <v>77</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="T35" t="s" s="2">
         <v>240</v>
@@ -5395,7 +5402,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>243</v>
@@ -5509,7 +5516,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>250</v>
@@ -5621,7 +5628,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>256</v>
@@ -5735,10 +5742,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5764,10 +5771,10 @@
         <v>227</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5798,7 +5805,7 @@
       </c>
       <c r="Y39" s="2"/>
       <c r="Z39" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>77</v>
@@ -5816,7 +5823,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -5840,15 +5847,15 @@
         <v>77</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5874,10 +5881,10 @@
         <v>227</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5908,7 +5915,7 @@
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>77</v>
@@ -5926,7 +5933,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -5941,7 +5948,7 @@
         <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>77</v>
@@ -5950,15 +5957,15 @@
         <v>77</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5984,10 +5991,10 @@
         <v>227</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6018,7 +6025,7 @@
       </c>
       <c r="Y41" s="2"/>
       <c r="Z41" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>77</v>
@@ -6036,7 +6043,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6060,15 +6067,15 @@
         <v>77</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6094,10 +6101,10 @@
         <v>227</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6124,11 +6131,11 @@
         <v>77</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>172</v>
+        <v>222</v>
       </c>
       <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>77</v>
@@ -6146,7 +6153,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6161,7 +6168,7 @@
         <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>77</v>
@@ -6170,15 +6177,15 @@
         <v>77</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6201,13 +6208,13 @@
         <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6258,7 +6265,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>88</v>
@@ -6287,10 +6294,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6316,10 +6323,10 @@
         <v>168</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6350,7 +6357,7 @@
       </c>
       <c r="Y44" s="2"/>
       <c r="Z44" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>77</v>
@@ -6368,7 +6375,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>88</v>
@@ -6383,13 +6390,13 @@
         <v>100</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>77</v>
@@ -6397,10 +6404,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6426,10 +6433,10 @@
         <v>102</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6509,10 +6516,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6619,13 +6626,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>77</v>
@@ -6647,13 +6654,13 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6719,7 +6726,7 @@
         <v>116</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>77</v>
@@ -6733,10 +6740,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6762,10 +6769,10 @@
         <v>102</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6816,7 +6823,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -6845,10 +6852,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6874,10 +6881,10 @@
         <v>123</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6928,7 +6935,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>88</v>
@@ -6943,24 +6950,24 @@
         <v>100</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6986,10 +6993,10 @@
         <v>123</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7040,7 +7047,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>88</v>
@@ -7055,24 +7062,24 @@
         <v>100</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7095,13 +7102,13 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7109,7 +7116,7 @@
         <v>77</v>
       </c>
       <c r="Q51" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="R51" t="s" s="2">
         <v>77</v>
@@ -7154,7 +7161,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7183,10 +7190,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7212,10 +7219,10 @@
         <v>102</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7266,7 +7273,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-slot-presence-absence.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-slot-presence-absence.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T13:38:26+00:00</t>
+    <t>2026-06-12T07:33:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-slot-presence-absence.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-slot-presence-absence.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T07:33:45+00:00</t>
+    <t>2026-06-12T07:50:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -680,9 +680,6 @@
 </t>
   </si>
   <si>
-    <t>idPresenceAbsenceUsager</t>
-  </si>
-  <si>
     <t>FiveWs.identifier</t>
   </si>
   <si>
@@ -844,6 +841,9 @@
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 SlotPresenceAbsenceIdentifierFormat:l'identifiant de la présence/absence doit respecter le format : 3+FINESS/identifiantLocalUsagerESSMS-PA-numPresenceAbsenceUsager {value.matches('^3[0-9]{9}/[A-Za-z0-9]+-PA-[A-Za-z0-9]+$')}</t>
+  </si>
+  <si>
+    <t>idPresenceAbsenceUsager</t>
   </si>
   <si>
     <t>Slot.identifier:idPA.id</t>
@@ -3790,24 +3790,24 @@
         <v>100</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN21" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="AL21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>214</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3916,10 +3916,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4030,10 +4030,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4059,16 +4059,16 @@
         <v>168</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="N24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -4093,29 +4093,29 @@
         <v>77</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF24" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="AA24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF24" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4133,7 +4133,7 @@
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
@@ -4144,10 +4144,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4170,19 +4170,19 @@
         <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>231</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4210,28 +4210,28 @@
         <v>150</v>
       </c>
       <c r="Y25" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="Z25" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="Z25" t="s" s="2">
+      <c r="AA25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4249,7 +4249,7 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -4260,10 +4260,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4289,16 +4289,16 @@
         <v>130</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4311,43 +4311,43 @@
         <v>77</v>
       </c>
       <c r="T26" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF26" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="U26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4365,7 +4365,7 @@
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4376,10 +4376,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4405,13 +4405,13 @@
         <v>102</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>246</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4425,43 +4425,43 @@
         <v>77</v>
       </c>
       <c r="T27" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="U27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4479,7 +4479,7 @@
         <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
@@ -4490,10 +4490,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4516,13 +4516,13 @@
         <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4573,7 +4573,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4591,7 +4591,7 @@
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
@@ -4602,10 +4602,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4628,16 +4628,16 @@
         <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4687,7 +4687,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4705,7 +4705,7 @@
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
@@ -4716,13 +4716,13 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>208</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>77</v>
@@ -4747,7 +4747,7 @@
         <v>209</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="M30" t="s" s="2">
         <v>211</v>
@@ -4813,11 +4813,11 @@
         <v>77</v>
       </c>
       <c r="AJ30" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AK30" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="AK30" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="AL30" t="s" s="2">
         <v>77</v>
       </c>
@@ -4825,7 +4825,7 @@
         <v>77</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="31">
@@ -4833,7 +4833,7 @@
         <v>267</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4945,7 +4945,7 @@
         <v>268</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5059,7 +5059,7 @@
         <v>269</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5085,16 +5085,16 @@
         <v>168</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="N33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5119,29 +5119,29 @@
         <v>77</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF33" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="AA33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5159,7 +5159,7 @@
         <v>77</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>77</v>
@@ -5173,7 +5173,7 @@
         <v>270</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5196,19 +5196,19 @@
         <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="N34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>231</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -5236,28 +5236,28 @@
         <v>150</v>
       </c>
       <c r="Y34" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="Z34" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="Z34" t="s" s="2">
+      <c r="AA34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF34" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="AA34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5275,7 +5275,7 @@
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
@@ -5289,7 +5289,7 @@
         <v>272</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5315,16 +5315,16 @@
         <v>130</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="N35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5337,43 +5337,43 @@
         <v>273</v>
       </c>
       <c r="T35" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF35" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="U35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5391,7 +5391,7 @@
         <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
@@ -5405,7 +5405,7 @@
         <v>274</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5431,13 +5431,13 @@
         <v>102</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>246</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5451,43 +5451,43 @@
         <v>77</v>
       </c>
       <c r="T36" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF36" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="U36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF36" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5505,7 +5505,7 @@
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
@@ -5519,7 +5519,7 @@
         <v>275</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5542,13 +5542,13 @@
         <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5599,7 +5599,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5617,7 +5617,7 @@
         <v>77</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>77</v>
@@ -5631,7 +5631,7 @@
         <v>276</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5654,16 +5654,16 @@
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5713,7 +5713,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5731,7 +5731,7 @@
         <v>77</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>77</v>
@@ -5768,7 +5768,7 @@
         <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L39" t="s" s="2">
         <v>278</v>
@@ -5878,7 +5878,7 @@
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L40" t="s" s="2">
         <v>283</v>
@@ -5911,7 +5911,7 @@
         <v>77</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
@@ -5988,7 +5988,7 @@
         <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L41" t="s" s="2">
         <v>288</v>
@@ -6021,7 +6021,7 @@
         <v>77</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Y41" s="2"/>
       <c r="Z41" t="s" s="2">
@@ -6098,7 +6098,7 @@
         <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L42" t="s" s="2">
         <v>292</v>
@@ -6131,7 +6131,7 @@
         <v>77</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
@@ -6353,7 +6353,7 @@
         <v>77</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Y44" s="2"/>
       <c r="Z44" t="s" s="2">

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-slot-presence-absence.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-slot-presence-absence.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1890" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1926" uniqueCount="342">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T07:50:14+00:00</t>
+    <t>2026-06-12T13:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -645,6 +645,19 @@
   </si>
   <si>
     <t>absencePrevue</t>
+  </si>
+  <si>
+    <t>Slot.extension:TDDUIFacturation</t>
+  </si>
+  <si>
+    <t>TDDUIFacturation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-facturation}
+</t>
+  </si>
+  <si>
+    <t>Indique si une facture a été établie.</t>
   </si>
   <si>
     <t>Slot.modifierExtension</t>
@@ -1366,7 +1379,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN52"/>
+  <dimension ref="A1:AN53"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="33.25" customWidth="true" bestFit="true"/>
@@ -3581,43 +3594,41 @@
         <v>203</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="C20" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="D20" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>108</v>
+        <v>205</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O20" t="s" s="2">
         <v>206</v>
       </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>77</v>
       </c>
@@ -3665,7 +3676,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3674,7 +3685,7 @@
         <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>77</v>
+        <v>201</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>116</v>
@@ -3683,7 +3694,7 @@
         <v>77</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>191</v>
+        <v>77</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>77</v>
@@ -3694,18 +3705,18 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>79</v>
@@ -3714,22 +3725,26 @@
         <v>77</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="N21" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O21" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="M21" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>77</v>
       </c>
@@ -3765,17 +3780,19 @@
         <v>77</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="AC21" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="AD21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3787,27 +3804,27 @@
         <v>77</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>77</v>
+        <v>191</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>213</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3815,10 +3832,10 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>77</v>
@@ -3827,16 +3844,16 @@
         <v>77</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>102</v>
+        <v>213</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>103</v>
+        <v>214</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>104</v>
+        <v>215</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3875,62 +3892,60 @@
         <v>77</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="AC22" s="2"/>
       <c r="AD22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>105</v>
+        <v>212</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>77</v>
+        <v>217</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>77</v>
@@ -3942,17 +3957,15 @@
         <v>77</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -3989,31 +4002,31 @@
         <v>77</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>77</v>
@@ -4030,46 +4043,44 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>168</v>
+        <v>108</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>217</v>
+        <v>109</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>218</v>
+        <v>110</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>220</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>77</v>
       </c>
@@ -4093,47 +4104,49 @@
         <v>77</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="Y24" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z24" t="s" s="2">
-        <v>222</v>
+        <v>77</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>223</v>
+        <v>115</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>224</v>
+        <v>85</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
@@ -4144,10 +4157,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4164,25 +4177,25 @@
         <v>77</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J25" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>226</v>
+        <v>168</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4207,13 +4220,11 @@
         <v>77</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>231</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>77</v>
@@ -4231,7 +4242,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4249,7 +4260,7 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -4260,10 +4271,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4286,19 +4297,19 @@
         <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>130</v>
+        <v>230</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4311,7 +4322,7 @@
         <v>77</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>239</v>
+        <v>77</v>
       </c>
       <c r="U26" t="s" s="2">
         <v>77</v>
@@ -4323,13 +4334,13 @@
         <v>77</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>77</v>
+        <v>235</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>77</v>
+        <v>236</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>77</v>
@@ -4347,7 +4358,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4365,7 +4376,7 @@
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4376,10 +4387,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4402,18 +4413,20 @@
         <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>102</v>
+        <v>130</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O27" s="2"/>
+        <v>241</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
       </c>
@@ -4425,7 +4438,7 @@
         <v>77</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="U27" t="s" s="2">
         <v>77</v>
@@ -4461,7 +4474,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4479,7 +4492,7 @@
         <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
@@ -4490,10 +4503,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4516,15 +4529,17 @@
         <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>250</v>
+        <v>102</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>77</v>
@@ -4537,7 +4552,7 @@
         <v>77</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>77</v>
+        <v>250</v>
       </c>
       <c r="U28" t="s" s="2">
         <v>77</v>
@@ -4573,7 +4588,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4591,7 +4606,7 @@
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
@@ -4602,10 +4617,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4628,17 +4643,15 @@
         <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="L29" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>259</v>
-      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>77</v>
@@ -4687,7 +4700,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4705,7 +4718,7 @@
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
@@ -4716,20 +4729,18 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="C30" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>88</v>
@@ -4744,15 +4755,17 @@
         <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>209</v>
+        <v>260</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>262</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -4801,47 +4814,49 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>208</v>
+        <v>264</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ30" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL30" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="AK30" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="AL30" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="AM30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>213</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="C31" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="B31" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>88</v>
@@ -4853,16 +4868,16 @@
         <v>77</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>102</v>
+        <v>213</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>103</v>
+        <v>268</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>104</v>
+        <v>215</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4913,50 +4928,50 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>105</v>
+        <v>212</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>77</v>
+        <v>269</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>77</v>
+        <v>270</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>77</v>
+        <v>217</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>77</v>
@@ -4968,17 +4983,15 @@
         <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>77</v>
@@ -5015,31 +5028,31 @@
         <v>77</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>77</v>
@@ -5056,46 +5069,44 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>168</v>
+        <v>108</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>217</v>
+        <v>109</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>218</v>
+        <v>110</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>220</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>77</v>
       </c>
@@ -5119,47 +5130,49 @@
         <v>77</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="Y33" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z33" t="s" s="2">
-        <v>222</v>
+        <v>77</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>223</v>
+        <v>115</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>224</v>
+        <v>85</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>77</v>
@@ -5170,10 +5183,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5181,7 +5194,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>88</v>
@@ -5190,25 +5203,25 @@
         <v>77</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J34" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>226</v>
+        <v>168</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -5218,7 +5231,7 @@
         <v>77</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>271</v>
+        <v>77</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>77</v>
@@ -5233,13 +5246,11 @@
         <v>77</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>231</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>77</v>
@@ -5257,7 +5268,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5275,7 +5286,7 @@
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
@@ -5286,10 +5297,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5312,19 +5323,19 @@
         <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>130</v>
+        <v>230</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5334,10 +5345,10 @@
         <v>77</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>239</v>
+        <v>77</v>
       </c>
       <c r="U35" t="s" s="2">
         <v>77</v>
@@ -5349,13 +5360,13 @@
         <v>77</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>77</v>
+        <v>235</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>77</v>
+        <v>236</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>77</v>
@@ -5373,7 +5384,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5391,7 +5402,7 @@
         <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
@@ -5402,10 +5413,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5428,18 +5439,20 @@
         <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>102</v>
+        <v>130</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O36" s="2"/>
+        <v>241</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>77</v>
       </c>
@@ -5448,10 +5461,10 @@
         <v>77</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>77</v>
+        <v>277</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="U36" t="s" s="2">
         <v>77</v>
@@ -5487,7 +5500,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5505,7 +5518,7 @@
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
@@ -5516,10 +5529,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5527,7 +5540,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>88</v>
@@ -5542,15 +5555,17 @@
         <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>250</v>
+        <v>102</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -5563,7 +5578,7 @@
         <v>77</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>77</v>
+        <v>250</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>77</v>
@@ -5599,7 +5614,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5617,7 +5632,7 @@
         <v>77</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>77</v>
@@ -5628,10 +5643,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5654,17 +5669,15 @@
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="L38" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>259</v>
-      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>77</v>
@@ -5713,7 +5726,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5731,7 +5744,7 @@
         <v>77</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>77</v>
@@ -5742,10 +5755,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>277</v>
+        <v>259</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5768,15 +5781,17 @@
         <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>226</v>
+        <v>260</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>278</v>
+        <v>261</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>262</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -5801,11 +5816,13 @@
         <v>77</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="Y39" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z39" t="s" s="2">
-        <v>280</v>
+        <v>77</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>77</v>
@@ -5823,13 +5840,13 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>77</v>
@@ -5841,21 +5858,21 @@
         <v>77</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>77</v>
+        <v>265</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>281</v>
+        <v>77</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5863,7 +5880,7 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>88</v>
@@ -5878,13 +5895,13 @@
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>284</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5911,11 +5928,11 @@
         <v>77</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>221</v>
+        <v>158</v>
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>77</v>
@@ -5933,7 +5950,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -5948,7 +5965,7 @@
         <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>286</v>
+        <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>77</v>
@@ -5957,15 +5974,15 @@
         <v>77</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5973,10 +5990,10 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>77</v>
@@ -5988,13 +6005,13 @@
         <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6021,11 +6038,11 @@
         <v>77</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="Y41" s="2"/>
       <c r="Z41" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>77</v>
@@ -6043,7 +6060,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6058,7 +6075,7 @@
         <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>77</v>
+        <v>290</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>77</v>
@@ -6067,7 +6084,7 @@
         <v>77</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="42">
@@ -6086,7 +6103,7 @@
         <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>77</v>
@@ -6098,7 +6115,7 @@
         <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="L42" t="s" s="2">
         <v>292</v>
@@ -6131,7 +6148,7 @@
         <v>77</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
@@ -6159,7 +6176,7 @@
         <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>77</v>
@@ -6168,7 +6185,7 @@
         <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>295</v>
+        <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>77</v>
@@ -6177,15 +6194,15 @@
         <v>77</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6193,7 +6210,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>88</v>
@@ -6208,13 +6225,13 @@
         <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="L43" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6241,13 +6258,11 @@
         <v>77</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y43" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="Y43" s="2"/>
       <c r="Z43" t="s" s="2">
-        <v>77</v>
+        <v>298</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>77</v>
@@ -6265,10 +6280,10 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>88</v>
@@ -6280,7 +6295,7 @@
         <v>100</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>77</v>
+        <v>299</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>77</v>
@@ -6289,7 +6304,7 @@
         <v>77</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>77</v>
+        <v>285</v>
       </c>
     </row>
     <row r="44">
@@ -6320,13 +6335,13 @@
         <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>168</v>
+        <v>301</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6353,11 +6368,13 @@
         <v>77</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="Y44" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z44" t="s" s="2">
-        <v>303</v>
+        <v>77</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>77</v>
@@ -6390,13 +6407,13 @@
         <v>100</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>304</v>
+        <v>77</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>305</v>
+        <v>77</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>77</v>
@@ -6404,10 +6421,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6415,7 +6432,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>88</v>
@@ -6427,16 +6444,16 @@
         <v>77</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>102</v>
+        <v>168</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6463,13 +6480,11 @@
         <v>77</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="Y45" s="2"/>
       <c r="Z45" t="s" s="2">
-        <v>77</v>
+        <v>307</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>77</v>
@@ -6487,10 +6502,10 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>105</v>
+        <v>304</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>88</v>
@@ -6499,16 +6514,16 @@
         <v>77</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>77</v>
+        <v>308</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>77</v>
+        <v>309</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>77</v>
@@ -6516,10 +6531,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6530,7 +6545,7 @@
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>77</v>
@@ -6542,13 +6557,13 @@
         <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>193</v>
+        <v>311</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>194</v>
+        <v>312</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6587,29 +6602,31 @@
         <v>77</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AC46" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="AD46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>77</v>
@@ -6626,14 +6643,12 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="C47" t="s" s="2">
-        <v>311</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
         <v>77</v>
       </c>
@@ -6642,7 +6657,7 @@
         <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>77</v>
@@ -6654,13 +6669,13 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>312</v>
+        <v>108</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>313</v>
+        <v>193</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>314</v>
+        <v>194</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6699,16 +6714,14 @@
         <v>77</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="AC47" s="2"/>
       <c r="AD47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AF47" t="s" s="2">
         <v>115</v>
@@ -6720,13 +6733,13 @@
         <v>79</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>201</v>
+        <v>77</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>116</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>315</v>
+        <v>77</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>77</v>
@@ -6740,12 +6753,14 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="C48" s="2"/>
+        <v>313</v>
+      </c>
+      <c r="C48" t="s" s="2">
+        <v>315</v>
+      </c>
       <c r="D48" t="s" s="2">
         <v>77</v>
       </c>
@@ -6766,13 +6781,13 @@
         <v>77</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>102</v>
+        <v>316</v>
       </c>
       <c r="L48" t="s" s="2">
         <v>317</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6823,22 +6838,22 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>318</v>
+        <v>115</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>77</v>
+        <v>201</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>77</v>
+        <v>319</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>77</v>
@@ -6852,10 +6867,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6863,7 +6878,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>88</v>
@@ -6875,13 +6890,13 @@
         <v>77</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M49" t="s" s="2">
         <v>321</v>
@@ -6935,10 +6950,10 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>88</v>
@@ -6947,27 +6962,27 @@
         <v>77</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>322</v>
+        <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>323</v>
+        <v>77</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>324</v>
+        <v>77</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6993,10 +7008,10 @@
         <v>123</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7047,7 +7062,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>88</v>
@@ -7062,24 +7077,24 @@
         <v>100</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>324</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7087,7 +7102,7 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>88</v>
@@ -7099,25 +7114,23 @@
         <v>77</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q51" t="s" s="2">
-        <v>334</v>
-      </c>
+      <c r="Q51" s="2"/>
       <c r="R51" t="s" s="2">
         <v>77</v>
       </c>
@@ -7161,10 +7174,10 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH51" t="s" s="2">
         <v>88</v>
@@ -7176,24 +7189,24 @@
         <v>100</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>77</v>
+        <v>332</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>77</v>
+        <v>333</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>77</v>
+        <v>328</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7216,7 +7229,7 @@
         <v>77</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>102</v>
+        <v>335</v>
       </c>
       <c r="L52" t="s" s="2">
         <v>336</v>
@@ -7229,7 +7242,9 @@
       <c r="P52" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q52" s="2"/>
+      <c r="Q52" t="s" s="2">
+        <v>338</v>
+      </c>
       <c r="R52" t="s" s="2">
         <v>77</v>
       </c>
@@ -7273,7 +7288,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7297,6 +7312,118 @@
         <v>77</v>
       </c>
       <c r="AN52" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
+      <c r="P53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN53" t="s" s="2">
         <v>77</v>
       </c>
     </row>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-slot-presence-absence.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-slot-presence-absence.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1926" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1926" uniqueCount="343">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T13:52:17+00:00</t>
+    <t>2026-06-15T09:04:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -658,6 +658,9 @@
   </si>
   <si>
     <t>Indique si une facture a été établie.</t>
+  </si>
+  <si>
+    <t>Statut.statut (pour le statut FACTURE)</t>
   </si>
   <si>
     <t>Slot.modifierExtension</t>
@@ -967,7 +970,7 @@
     <t>Slot.status</t>
   </si>
   <si>
-    <t>busy | free | busy-unavailable | busy-tentative | entered-in-error</t>
+    <t>Correspondance des statuts métier avec les codes FHIR : PLANIFIE → busy-tentative, VALIDE → busy. Le statut FACTURE est couvert par l'extension TDDUIFacturation.</t>
   </si>
   <si>
     <t>busy | free | busy-unavailable | busy-tentative | entered-in-error.</t>
@@ -976,7 +979,7 @@
     <t>http://hl7.org/fhir/ValueSet/slotstatus</t>
   </si>
   <si>
-    <t>Statut.statut</t>
+    <t>Statut.statut (pour les statuts PLANIFIE et VALIDE)</t>
   </si>
   <si>
     <t>FREEBUSY;FBTYPE=(freeBusyType):19980314T233000Z/19980315T003000Z If the freeBusyType is BUSY, then this value can be excluded</t>
@@ -1417,7 +1420,7 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="30.4765625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="40.49609375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="87.9765625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="110.453125" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
@@ -3691,7 +3694,7 @@
         <v>116</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>77</v>
+        <v>207</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>77</v>
@@ -3705,10 +3708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3734,16 +3737,16 @@
         <v>108</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>77</v>
@@ -3792,7 +3795,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3821,10 +3824,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3847,13 +3850,13 @@
         <v>89</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3892,7 +3895,7 @@
         <v>77</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC22" s="2"/>
       <c r="AD22" t="s" s="2">
@@ -3902,7 +3905,7 @@
         <v>114</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -3926,15 +3929,15 @@
         <v>77</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4043,10 +4046,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4157,10 +4160,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4186,16 +4189,16 @@
         <v>168</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4220,11 +4223,11 @@
         <v>77</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>77</v>
@@ -4242,7 +4245,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4260,7 +4263,7 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -4271,10 +4274,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4297,19 +4300,19 @@
         <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4337,10 +4340,10 @@
         <v>150</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>77</v>
@@ -4358,7 +4361,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4376,7 +4379,7 @@
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4387,10 +4390,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4416,16 +4419,16 @@
         <v>130</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4438,7 +4441,7 @@
         <v>77</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="U27" t="s" s="2">
         <v>77</v>
@@ -4474,7 +4477,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4492,7 +4495,7 @@
         <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
@@ -4503,10 +4506,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4532,13 +4535,13 @@
         <v>102</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4552,7 +4555,7 @@
         <v>77</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="U28" t="s" s="2">
         <v>77</v>
@@ -4588,7 +4591,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4606,7 +4609,7 @@
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
@@ -4617,10 +4620,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4643,13 +4646,13 @@
         <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4700,7 +4703,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4718,7 +4721,7 @@
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
@@ -4729,10 +4732,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4755,16 +4758,16 @@
         <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4814,7 +4817,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4832,7 +4835,7 @@
         <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>77</v>
@@ -4843,13 +4846,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>77</v>
@@ -4871,13 +4874,13 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4928,7 +4931,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -4940,10 +4943,10 @@
         <v>77</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>77</v>
@@ -4952,15 +4955,15 @@
         <v>77</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5069,10 +5072,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5183,10 +5186,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5212,16 +5215,16 @@
         <v>168</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -5246,11 +5249,11 @@
         <v>77</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>77</v>
@@ -5268,7 +5271,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5286,7 +5289,7 @@
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
@@ -5297,10 +5300,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5323,19 +5326,19 @@
         <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5345,7 +5348,7 @@
         <v>77</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="T35" t="s" s="2">
         <v>77</v>
@@ -5363,10 +5366,10 @@
         <v>150</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>77</v>
@@ -5384,7 +5387,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5402,7 +5405,7 @@
         <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
@@ -5413,10 +5416,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5442,16 +5445,16 @@
         <v>130</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5461,10 +5464,10 @@
         <v>77</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="U36" t="s" s="2">
         <v>77</v>
@@ -5500,7 +5503,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5518,7 +5521,7 @@
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
@@ -5529,10 +5532,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5558,13 +5561,13 @@
         <v>102</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5578,7 +5581,7 @@
         <v>77</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>77</v>
@@ -5614,7 +5617,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5632,7 +5635,7 @@
         <v>77</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>77</v>
@@ -5643,10 +5646,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5669,13 +5672,13 @@
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5726,7 +5729,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5744,7 +5747,7 @@
         <v>77</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>77</v>
@@ -5755,10 +5758,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5781,16 +5784,16 @@
         <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5840,7 +5843,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -5858,7 +5861,7 @@
         <v>77</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>77</v>
@@ -5869,10 +5872,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5895,13 +5898,13 @@
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5932,7 +5935,7 @@
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>77</v>
@@ -5950,7 +5953,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -5974,15 +5977,15 @@
         <v>77</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6005,13 +6008,13 @@
         <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6038,11 +6041,11 @@
         <v>77</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Y41" s="2"/>
       <c r="Z41" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>77</v>
@@ -6060,7 +6063,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6075,7 +6078,7 @@
         <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>77</v>
@@ -6084,15 +6087,15 @@
         <v>77</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6115,13 +6118,13 @@
         <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6148,11 +6151,11 @@
         <v>77</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>77</v>
@@ -6170,7 +6173,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6194,15 +6197,15 @@
         <v>77</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6225,13 +6228,13 @@
         <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6258,11 +6261,11 @@
         <v>77</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Y43" s="2"/>
       <c r="Z43" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>77</v>
@@ -6280,7 +6283,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6295,7 +6298,7 @@
         <v>100</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>77</v>
@@ -6304,15 +6307,15 @@
         <v>77</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6335,13 +6338,13 @@
         <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6392,7 +6395,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>88</v>
@@ -6421,10 +6424,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6450,10 +6453,10 @@
         <v>168</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6480,11 +6483,11 @@
         <v>77</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Y45" s="2"/>
       <c r="Z45" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>77</v>
@@ -6502,7 +6505,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>88</v>
@@ -6517,13 +6520,13 @@
         <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>77</v>
@@ -6531,10 +6534,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6560,10 +6563,10 @@
         <v>102</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6643,10 +6646,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6753,13 +6756,13 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="B48" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="B48" t="s" s="2">
-        <v>313</v>
-      </c>
       <c r="C48" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>77</v>
@@ -6781,13 +6784,13 @@
         <v>77</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6853,7 +6856,7 @@
         <v>116</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>77</v>
@@ -6867,10 +6870,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6896,10 +6899,10 @@
         <v>102</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6950,7 +6953,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -6979,10 +6982,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7008,10 +7011,10 @@
         <v>123</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7062,7 +7065,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>88</v>
@@ -7077,24 +7080,24 @@
         <v>100</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7120,10 +7123,10 @@
         <v>123</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7174,7 +7177,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>88</v>
@@ -7189,24 +7192,24 @@
         <v>100</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7229,13 +7232,13 @@
         <v>77</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7243,7 +7246,7 @@
         <v>77</v>
       </c>
       <c r="Q52" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="R52" t="s" s="2">
         <v>77</v>
@@ -7288,7 +7291,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7317,10 +7320,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7346,10 +7349,10 @@
         <v>102</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7400,7 +7403,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-slot-presence-absence.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-slot-presence-absence.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T09:04:15+00:00</t>
+    <t>2026-06-16T10:03:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -266,7 +266,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}motifAbsenceCardinality:Cet attribut est obligatoire pour les typePresenceAbsence=Absence {(serviceType.coding.code='2') implies (appointmentType.exists())}absencePrevueCardinality:Cet attribut est obligatoire pour les typePresenceAbsence=Absence {(serviceType.coding.code='2') implies (extension[TDDUIPlannedAbsence].exists())}</t>
   </si>
   <si>
     <t>PresenceAbsence</t>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-slot-presence-absence.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-slot-presence-absence.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T10:03:26+00:00</t>
+    <t>2026-06-16T13:10:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>
@@ -266,7 +266,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}motifAbsenceCardinality:Cet attribut est obligatoire pour les typePresenceAbsence=Absence {(serviceType.coding.code='2') implies (appointmentType.exists())}absencePrevueCardinality:Cet attribut est obligatoire pour les typePresenceAbsence=Absence {(serviceType.coding.code='2') implies (extension[TDDUIPlannedAbsence].exists())}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}motifAbsenceCardinality:Cet attribut est obligatoire pour les typePresenceAbsence=Absence {(serviceType.coding.code='2') implies (appointmentType.exists())}absencePrevueCardinality:Cet attribut est obligatoire pour les typePresenceAbsence=Absence {(serviceType.coding.code='2') implies (extension.where(url = 'https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-planned-absence').exists())}</t>
   </si>
   <si>
     <t>PresenceAbsence</t>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-slot-presence-absence.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-slot-presence-absence.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1926" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1924" uniqueCount="342">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T13:10:49+00:00</t>
+    <t>2026-06-22T08:40:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -266,7 +266,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}motifAbsenceCardinality:Cet attribut est obligatoire pour les typePresenceAbsence=Absence {(serviceType.coding.code='2') implies (appointmentType.exists())}absencePrevueCardinality:Cet attribut est obligatoire pour les typePresenceAbsence=Absence {(serviceType.coding.code='2') implies (extension.where(url = 'https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-planned-absence').exists())}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}motifAbsenceCardinality:motifAbsence est obligatoire pour les typePresenceAbsence=Absence {(serviceType.coding.code='2') implies (appointmentType.exists())}absencePrevueCardinality:absencePrevue est obligatoire pour les typePresenceAbsence=Absence {(serviceType.coding.code='2') implies (extension.where(url = 'https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-planned-absence').exists())}</t>
   </si>
   <si>
     <t>PresenceAbsence</t>
@@ -751,10 +751,7 @@
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
-    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-slot-identifier-presence-absence</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -1410,7 +1407,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="60.9453125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="71.83984375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -4337,31 +4334,29 @@
         <v>77</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="Y26" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="Y26" s="2"/>
+      <c r="Z26" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="Z26" t="s" s="2">
+      <c r="AA26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF26" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4390,10 +4385,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4419,16 +4414,16 @@
         <v>130</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4441,43 +4436,43 @@
         <v>77</v>
       </c>
       <c r="T27" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="U27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4495,7 +4490,7 @@
         <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
@@ -4506,10 +4501,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4535,13 +4530,13 @@
         <v>102</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4555,43 +4550,43 @@
         <v>77</v>
       </c>
       <c r="T28" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="U28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF28" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="U28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4609,7 +4604,7 @@
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
@@ -4620,10 +4615,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4646,13 +4641,13 @@
         <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4703,7 +4698,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4721,7 +4716,7 @@
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
@@ -4732,10 +4727,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4758,16 +4753,16 @@
         <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>264</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4817,7 +4812,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4835,7 +4830,7 @@
         <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>77</v>
@@ -4846,13 +4841,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>213</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>77</v>
@@ -4877,7 +4872,7 @@
         <v>214</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="M31" t="s" s="2">
         <v>216</v>
@@ -4943,10 +4938,10 @@
         <v>77</v>
       </c>
       <c r="AJ31" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AK31" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="AK31" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>77</v>
@@ -4960,7 +4955,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>219</v>
@@ -5072,7 +5067,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>220</v>
@@ -5186,7 +5181,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>221</v>
@@ -5300,7 +5295,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>230</v>
@@ -5348,7 +5343,7 @@
         <v>77</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="T35" t="s" s="2">
         <v>77</v>
@@ -5363,31 +5358,29 @@
         <v>77</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="Y35" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="Y35" s="2"/>
+      <c r="Z35" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="Z35" t="s" s="2">
+      <c r="AA35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF35" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5416,10 +5409,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5445,16 +5438,16 @@
         <v>130</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="N36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5464,46 +5457,46 @@
         <v>77</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="T36" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF36" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="U36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF36" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5521,7 +5514,7 @@
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
@@ -5532,10 +5525,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5561,13 +5554,13 @@
         <v>102</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5581,43 +5574,43 @@
         <v>77</v>
       </c>
       <c r="T37" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF37" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="U37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5635,7 +5628,7 @@
         <v>77</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>77</v>
@@ -5646,10 +5639,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5672,13 +5665,13 @@
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5729,7 +5722,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5747,7 +5740,7 @@
         <v>77</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>77</v>
@@ -5758,10 +5751,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5784,16 +5777,16 @@
         <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>264</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5843,7 +5836,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -5861,7 +5854,7 @@
         <v>77</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>77</v>
@@ -5872,10 +5865,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5901,10 +5894,10 @@
         <v>231</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>284</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5935,7 +5928,7 @@
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>77</v>
@@ -5953,7 +5946,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -5977,15 +5970,15 @@
         <v>77</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6011,10 +6004,10 @@
         <v>231</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6045,7 +6038,7 @@
       </c>
       <c r="Y41" s="2"/>
       <c r="Z41" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>77</v>
@@ -6063,7 +6056,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6078,7 +6071,7 @@
         <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>77</v>
@@ -6087,15 +6080,15 @@
         <v>77</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6121,10 +6114,10 @@
         <v>231</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>294</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6155,7 +6148,7 @@
       </c>
       <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>77</v>
@@ -6173,7 +6166,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6197,15 +6190,15 @@
         <v>77</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6231,10 +6224,10 @@
         <v>231</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6265,7 +6258,7 @@
       </c>
       <c r="Y43" s="2"/>
       <c r="Z43" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>77</v>
@@ -6283,7 +6276,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6298,7 +6291,7 @@
         <v>100</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>77</v>
@@ -6307,15 +6300,15 @@
         <v>77</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6338,13 +6331,13 @@
         <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6395,7 +6388,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>88</v>
@@ -6424,10 +6417,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6453,10 +6446,10 @@
         <v>168</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6487,7 +6480,7 @@
       </c>
       <c r="Y45" s="2"/>
       <c r="Z45" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>77</v>
@@ -6505,7 +6498,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>88</v>
@@ -6520,13 +6513,13 @@
         <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM45" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>77</v>
@@ -6534,10 +6527,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6563,10 +6556,10 @@
         <v>102</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6646,10 +6639,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6756,13 +6749,13 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="C48" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="C48" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>77</v>
@@ -6784,13 +6777,13 @@
         <v>77</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6856,7 +6849,7 @@
         <v>116</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>77</v>
@@ -6870,10 +6863,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6899,10 +6892,10 @@
         <v>102</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6953,7 +6946,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -6982,10 +6975,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7011,10 +7004,10 @@
         <v>123</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7065,7 +7058,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>88</v>
@@ -7080,24 +7073,24 @@
         <v>100</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM50" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="AL50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM50" t="s" s="2">
+      <c r="AN50" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>329</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7123,10 +7116,10 @@
         <v>123</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>332</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7177,7 +7170,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>88</v>
@@ -7192,24 +7185,24 @@
         <v>100</v>
       </c>
       <c r="AK51" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="AL51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>334</v>
-      </c>
       <c r="AN51" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7232,13 +7225,13 @@
         <v>77</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>338</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7246,7 +7239,7 @@
         <v>77</v>
       </c>
       <c r="Q52" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="R52" t="s" s="2">
         <v>77</v>
@@ -7291,7 +7284,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7320,10 +7313,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7349,10 +7342,10 @@
         <v>102</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7403,7 +7396,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-slot-presence-absence.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-slot-presence-absence.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T08:40:39+00:00</t>
+    <t>2026-06-24T07:42:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
